--- a/themes/documents.xlsx
+++ b/themes/documents.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -450,81 +450,21 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  isNotAuthorized: Для уточнения статуса рассмотрения документов напишите в чат приложения «Уралсиб Онлайн» или его [веб-версии](https://online.uralsib.ru/)</t>
+          <t xml:space="preserve">  isNotAuthorized: Для уточнения информации по разблокировке карты  напишите в чат приложения «Уралсиб Онлайн» или его [веб-версии](https://online.uralsib.ru/)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  isNotAuthorized: Для уточнения статуса рассмотрения документов напишите в чат приложения «Уралсиб Онлайн» или его [веб-версии](https://online.uralsib.ru/).</t>
+          <t xml:space="preserve">  isNotAuthorized: Для уточнения информации по разблокировке карты напишите в чат приложения «Уралсиб Онлайн» или его [веб-версии](https://online.uralsib.ru/)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>59</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    - Если в заявке не удается прикрепить документ, подтверждающий доход, обновите приложение «Уралсиб Онлайн» или воспользуйтесь [веб-версией](https://online.uralsib.ru/)</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    - Если в заявке не удается прикрепить документ, подтверждающий доход, обновите приложение «Уралсиб Онлайн» или воспользуйтесь [веб-версией](https://online.uralsib.ru/).</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>60</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    - Выписку СФР нужно отправить с портала Госуслуги на pfr@uralsib.ru</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    - Выписку СФР нужно отправить с портала Госуслуги на pfr@uralsib.ru.</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>77</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  isNotAuthorized: Для уточнения информации по разблокировке карты  напишите в чат приложения «Уралсиб Онлайн» или его [веб-версии](https://online.uralsib.ru/)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  isNotAuthorized: Для уточнения информации по разблокировке карты напишите в чат приложения «Уралсиб Онлайн» или его [веб-версии](https://online.uralsib.ru/).</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>убран двойной пробел; добавлена точка в конце предложения</t>
+          <t>убран двойной пробел</t>
         </is>
       </c>
     </row>
